--- a/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_d_deptot_a_2018.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_d_deptot_a_2018.xlsx
@@ -99,7 +99,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 13:43</t>
+    <t xml:space="preserve">2026-09-24 00:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -519,10 +519,10 @@
         <v>5</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>-0.35</v>
+        <v>-0.34</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="3">
@@ -536,7 +536,7 @@
         <v>-0.55</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="4">
@@ -550,7 +550,7 @@
         <v>-0.27</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="5">
@@ -564,7 +564,7 @@
         <v>0.21</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="6">
@@ -578,7 +578,7 @@
         <v>0.36</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="7">
@@ -589,10 +589,10 @@
         <v>11</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="8">
@@ -603,10 +603,10 @@
         <v>11</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="9">
@@ -617,10 +617,10 @@
         <v>11</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0.09</v>
+        <v>0.07</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="10">
@@ -634,7 +634,7 @@
         <v>0.13</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="11">
@@ -648,7 +648,7 @@
         <v>0.12</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="12">
@@ -662,7 +662,7 @@
         <v>0.2</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="13">
@@ -676,7 +676,7 @@
         <v>0.24</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="14">
@@ -690,7 +690,7 @@
         <v>0.07</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="15">
@@ -704,7 +704,7 @@
         <v>-0.05</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="16">
@@ -715,10 +715,10 @@
         <v>11</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>-0.29</v>
+        <v>-0.3</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="17">
@@ -732,7 +732,7 @@
         <v>-0.38</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="18">
@@ -746,7 +746,7 @@
         <v>-0.77</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_d_deptot_a_2018.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_d_deptot_a_2018.xlsx
@@ -99,7 +99,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:34</t>
+    <t xml:space="preserve">2026-10-01 23:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_d_deptot_a_2018.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_d_deptot_a_2018.xlsx
@@ -99,7 +99,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:05</t>
+    <t xml:space="preserve">2026-10-05 19:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
